--- a/Data/Building/TeaRoom.Temperature.xlsx
+++ b/Data/Building/TeaRoom.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709235908</v>
+        <v>1711829065</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709262629</v>
+        <v>1711855521</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709269873</v>
+        <v>1711861449</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709282764</v>
+        <v>1711866643</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,15 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709223720</v>
+        <v>1711877092</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709234698</v>
+        <v>1711907551</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709260062</v>
+        <v>1711917343</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709268795</v>
+        <v>1711934326</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +741,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709315337</v>
+        <v>1711938848</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +770,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709325904</v>
+        <v>1711945961</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +803,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709343348</v>
+        <v>1711949087</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +840,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709350116</v>
+        <v>1711989671</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709354560</v>
+        <v>1711997277</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709361432</v>
+        <v>1712006580</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +939,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709396814</v>
+        <v>1712025283</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +980,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709401433</v>
+        <v>1712034331</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1009,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709428179</v>
+        <v>1712079882</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1046,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709434844</v>
+        <v>1712089188</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1075,15 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1102,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709446678</v>
+        <v>1712109649</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1112,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1135,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709483362</v>
+        <v>1712116340</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1149,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1168,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709490533</v>
+        <v>1712125013</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1178,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1201,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709499792</v>
+        <v>1712129940</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1211,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1234,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709517044</v>
+        <v>1712162115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1248,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1267,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709526794</v>
+        <v>1712167803</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1277,15 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1304,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709573028</v>
+        <v>1712192354</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1318,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1337,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709582214</v>
+        <v>1712199602</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1347,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1370,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709602532</v>
+        <v>1712206087</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1380,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1403,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709609986</v>
+        <v>1712214640</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1417,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1436,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709616175</v>
+        <v>1712253788</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1446,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1469,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709623551</v>
+        <v>1712263295</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1479,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1506,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709661038</v>
+        <v>1712281045</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1520,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1539,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709671125</v>
+        <v>1712290620</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1549,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1572,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709689962</v>
+        <v>1712338228</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1586,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1605,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709698716</v>
+        <v>1712347392</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1615,15 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1642,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709708765</v>
+        <v>1712367871</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1652,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1675,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709719150</v>
+        <v>1712377039</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1689,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1708,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709750223</v>
+        <v>1712386274</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1718,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1741,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709760422</v>
+        <v>1712398630</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1751,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1774,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709781058</v>
+        <v>1712425854</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1788,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1807,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709791119</v>
+        <v>1712435123</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1817,15 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1844,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709833300</v>
+        <v>1712456335</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1858,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1877,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709843306</v>
+        <v>1712464457</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1887,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1910,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709859693</v>
+        <v>1712473629</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1920,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1943,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709866191</v>
+        <v>1712485893</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1957,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1976,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709871835</v>
+        <v>1712512512</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1986,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2009,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709877823</v>
+        <v>1712521693</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2019,15 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2046,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709919526</v>
+        <v>1712539930</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2060,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2079,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709928922</v>
+        <v>1712546272</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2089,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2112,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709947141</v>
+        <v>1712550901</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2122,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2145,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709952121</v>
+        <v>1712561400</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2159,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2178,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709959457</v>
+        <v>1712597677</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2188,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2211,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709966156</v>
+        <v>1712606765</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2221,15 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2248,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710006542</v>
+        <v>1712625857</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2262,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2281,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710016310</v>
+        <v>1712631711</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2291,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2314,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710032479</v>
+        <v>1712636821</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2324,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2347,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710041634</v>
+        <v>1712644420</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2361,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2380,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710050842</v>
+        <v>1712685835</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2390,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2413,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710054198</v>
+        <v>1712697291</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2423,15 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2450,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710088156</v>
+        <v>1712719006</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2464,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2483,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710094253</v>
+        <v>1712727982</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2493,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2516,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710122245</v>
+        <v>1712770939</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2530,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2549,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710129416</v>
+        <v>1712780027</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2559,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2586,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710182602</v>
+        <v>1712802705</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2600,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2619,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710192240</v>
+        <v>1712808359</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2629,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2652,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710206237</v>
+        <v>1712859827</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2666,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2685,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710210264</v>
+        <v>1712869008</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2695,15 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2722,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710222030</v>
+        <v>1712885620</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2732,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2755,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710226916</v>
+        <v>1712892237</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2769,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2788,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710262293</v>
+        <v>1712941573</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2802,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2821,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710266410</v>
+        <v>1712945002</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2835,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2858,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710290431</v>
+        <v>1712968561</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2872,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2891,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710296299</v>
+        <v>1712972541</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2905,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2924,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710310051</v>
+        <v>1712988887</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2938,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2957,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710323409</v>
+        <v>1712999800</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2971,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2990,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710353607</v>
+        <v>1713030598</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3004,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3023,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710362784</v>
+        <v>1713040015</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3037,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3060,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710385466</v>
+        <v>1713060121</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3074,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3093,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710388740</v>
+        <v>1713067561</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3107,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3126,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710437627</v>
+        <v>1713077361</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3136,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3159,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710446904</v>
+        <v>1713088552</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3169,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3192,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710465630</v>
+        <v>1713118462</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3206,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3225,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710472630</v>
+        <v>1713127995</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3235,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3262,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710522377</v>
+        <v>1713146770</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3276,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3295,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710525829</v>
+        <v>1713154589</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3305,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3328,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710550315</v>
+        <v>1713202834</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3342,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3361,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710555349</v>
+        <v>1713212375</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3371,15 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3398,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710562476</v>
+        <v>1713229512</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3408,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3431,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710572934</v>
+        <v>1713236166</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3445,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3464,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710611016</v>
+        <v>1713239666</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3474,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3497,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710620474</v>
+        <v>1713250275</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3507,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3530,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710640231</v>
+        <v>1713289936</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3544,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3563,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710646526</v>
+        <v>1713299293</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3573,15 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3600,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710701298</v>
+        <v>1713316549</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3614,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3633,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710711394</v>
+        <v>1713323322</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3643,11 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3666,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710723245</v>
+        <v>1713327911</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3676,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3699,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710730778</v>
+        <v>1713370022</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3713,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3732,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710736649</v>
+        <v>1713378288</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3742,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3765,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710742807</v>
+        <v>1713387906</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3775,15 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3802,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710783948</v>
+        <v>1713403997</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3816,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3835,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710793121</v>
+        <v>1713412321</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3845,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3868,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710812058</v>
+        <v>1713457085</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3882,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3901,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710818130</v>
+        <v>1713462979</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3911,15 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3938,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710827476</v>
+        <v>1713490487</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3948,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3971,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710865264</v>
+        <v>1713494179</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3985,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4004,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710875058</v>
+        <v>1713547077</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4018,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4037,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710895852</v>
+        <v>1713550564</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4047,15 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4074,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710901150</v>
+        <v>1713574585</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4084,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4107,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710910076</v>
+        <v>1713583295</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4117,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyHot</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4140,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710929223</v>
+        <v>1713592495</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4154,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4173,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710957324</v>
+        <v>1713629230</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4187,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4206,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710966986</v>
+        <v>1713635144</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4220,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710986900</v>
+        <v>1713644548</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4249,15 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4276,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710995362</v>
+        <v>1713662954</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4286,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4309,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711004932</v>
+        <v>1713671432</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4319,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyHot</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4342,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711016615</v>
+        <v>1713716751</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4352,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4375,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711045602</v>
+        <v>1713726099</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4385,15 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4412,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711055278</v>
+        <v>1713748744</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4426,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4445,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711073862</v>
+        <v>1713754016</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4459,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4478,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711079902</v>
+        <v>1713759359</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4492,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4511,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711129315</v>
+        <v>1713765096</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4525,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4544,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711138510</v>
+        <v>1713802858</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4558,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4577,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711156440</v>
+        <v>1713812286</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4587,15 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4614,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711163547</v>
+        <v>1713836666</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4624,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4647,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711171617</v>
+        <v>1713840127</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4657,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyHot</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4680,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711180797</v>
+        <v>1713893453</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4690,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4713,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711216202</v>
+        <v>1713902474</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4723,15 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4750,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711226090</v>
+        <v>1713921687</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4764,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4783,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711241409</v>
+        <v>1713927640</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4797,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4816,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711255416</v>
+        <v>1713931091</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4830,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4849,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711262820</v>
+        <v>1713974574</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4863,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4882,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711297778</v>
+        <v>1713983114</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4896,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4915,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711304463</v>
+        <v>1713992507</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4929,11 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4952,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711329898</v>
+        <v>1714006977</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4966,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4985,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711336614</v>
+        <v>1714016217</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4999,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5018,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711340909</v>
+        <v>1714068803</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5028,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5051,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711383207</v>
+        <v>1714078616</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5061,15 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5088,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711389509</v>
+        <v>1714093913</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5102,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5121,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711399070</v>
+        <v>1714101730</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5131,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5154,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711416917</v>
+        <v>1714153216</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5168,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5187,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711424030</v>
+        <v>1714162685</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5197,15 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5224,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711430526</v>
+        <v>1714181678</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5234,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5257,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711437956</v>
+        <v>1714189059</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5271,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5290,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711475747</v>
+        <v>1714198321</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5300,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5323,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711484988</v>
+        <v>1714233779</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5333,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5356,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711505643</v>
+        <v>1714240087</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5370,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5389,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711513717</v>
+        <v>1714249511</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5399,15 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
+          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5426,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711523010</v>
+        <v>1714267824</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5436,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
+          <t>TeaRoom.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5459,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711555397</v>
+        <v>1714275720</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5473,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5492,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711562440</v>
+        <v>1714285038</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5502,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
+          <t>TeaRoom.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5525,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711571651</v>
+        <v>1714292892</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,138 +5535,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>TeaRoom.Temperature.state: ExcessivelyCold</t>
+          <t>TeaRoom.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>1711592616</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>TeaRoom.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>1711601371</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1711610456</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>TeaRoom.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>TeaRoom</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1711621294</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>TeaRoom.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
